--- a/data/gravel/Sage Storm King 2025.xlsx
+++ b/data/gravel/Sage Storm King 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF681F51-CABF-FD4F-A8A5-5A85E9BA6EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB45FCE-8551-E240-9A32-491BC9B4E7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28560" yWindow="-19440" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11160" yWindow="640" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="129">
   <si>
     <t>brand</t>
   </si>
@@ -222,9 +222,6 @@
   </si>
   <si>
     <t>suspension_corrected</t>
-  </si>
-  <si>
-    <t>40</t>
   </si>
   <si>
     <t>fork_suspension</t>
@@ -780,7 +777,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
@@ -804,12 +801,12 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
@@ -825,58 +822,58 @@
         <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" t="s">
         <v>117</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>118</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>119</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>120</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>121</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>122</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>123</v>
       </c>
-      <c r="J8" t="s">
-        <v>124</v>
-      </c>
       <c r="L8" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M8" t="s">
+        <v>116</v>
+      </c>
+      <c r="N8" t="s">
         <v>117</v>
       </c>
-      <c r="N8" t="s">
+      <c r="O8" t="s">
         <v>118</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>119</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>120</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>121</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>122</v>
       </c>
-      <c r="S8" t="s">
+      <c r="T8" t="s">
         <v>123</v>
-      </c>
-      <c r="T8" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
@@ -887,35 +884,35 @@
         <v>12</v>
       </c>
       <c r="C9">
-        <f>M9*10</f>
+        <f t="shared" ref="C9:J10" si="0">M9*10</f>
         <v>450</v>
       </c>
       <c r="D9">
-        <f>N9*10</f>
+        <f t="shared" si="0"/>
         <v>470</v>
       </c>
       <c r="E9">
-        <f>O9*10</f>
+        <f t="shared" si="0"/>
         <v>490</v>
       </c>
       <c r="F9">
-        <f>P9*10</f>
+        <f t="shared" si="0"/>
         <v>510</v>
       </c>
       <c r="G9">
-        <f>Q9*10</f>
+        <f t="shared" si="0"/>
         <v>520</v>
       </c>
       <c r="H9">
-        <f>R9*10</f>
+        <f t="shared" si="0"/>
         <v>540</v>
       </c>
       <c r="I9">
-        <f>S9*10</f>
+        <f t="shared" si="0"/>
         <v>560</v>
       </c>
       <c r="J9">
-        <f>T9*10</f>
+        <f t="shared" si="0"/>
         <v>575</v>
       </c>
       <c r="L9" t="s">
@@ -954,35 +951,35 @@
         <v>14</v>
       </c>
       <c r="C10">
-        <f>M10*10</f>
+        <f t="shared" si="0"/>
         <v>539</v>
       </c>
       <c r="D10">
-        <f>N10*10</f>
+        <f t="shared" si="0"/>
         <v>541.59999999999991</v>
       </c>
       <c r="E10">
-        <f>O10*10</f>
+        <f t="shared" si="0"/>
         <v>555.20000000000005</v>
       </c>
       <c r="F10">
-        <f>P10*10</f>
+        <f t="shared" si="0"/>
         <v>569.29999999999995</v>
       </c>
       <c r="G10">
-        <f>Q10*10</f>
+        <f t="shared" si="0"/>
         <v>569.70000000000005</v>
       </c>
       <c r="H10">
-        <f>R10*10</f>
+        <f t="shared" si="0"/>
         <v>595.70000000000005</v>
       </c>
       <c r="I10">
-        <f>S10*10</f>
+        <f t="shared" si="0"/>
         <v>614.5</v>
       </c>
       <c r="J10">
-        <f>T10*10</f>
+        <f t="shared" si="0"/>
         <v>635.79999999999995</v>
       </c>
       <c r="L10" t="s">
@@ -1021,35 +1018,35 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <f>M11</f>
+        <f t="shared" ref="C11:J13" si="1">M11</f>
         <v>70.25</v>
       </c>
       <c r="D11">
-        <f>N11</f>
+        <f t="shared" si="1"/>
         <v>70.25</v>
       </c>
       <c r="E11">
-        <f>O11</f>
+        <f t="shared" si="1"/>
         <v>70.5</v>
       </c>
       <c r="F11">
-        <f>P11</f>
+        <f t="shared" si="1"/>
         <v>71.25</v>
       </c>
       <c r="G11">
-        <f>Q11</f>
+        <f t="shared" si="1"/>
         <v>71</v>
       </c>
       <c r="H11">
-        <f>R11</f>
+        <f t="shared" si="1"/>
         <v>71.25</v>
       </c>
       <c r="I11">
-        <f>S11</f>
+        <f t="shared" si="1"/>
         <v>71.75</v>
       </c>
       <c r="J11">
-        <f>T11</f>
+        <f t="shared" si="1"/>
         <v>71.75</v>
       </c>
       <c r="L11" t="s">
@@ -1088,35 +1085,35 @@
         <v>18</v>
       </c>
       <c r="C12">
-        <f>M12</f>
+        <f t="shared" si="1"/>
         <v>72.75</v>
       </c>
       <c r="D12">
-        <f>N12</f>
+        <f t="shared" si="1"/>
         <v>73.5</v>
       </c>
       <c r="E12">
-        <f>O12</f>
+        <f t="shared" si="1"/>
         <v>73</v>
       </c>
       <c r="F12">
-        <f>P12</f>
+        <f t="shared" si="1"/>
         <v>72.5</v>
       </c>
       <c r="G12">
-        <f>Q12</f>
+        <f t="shared" si="1"/>
         <v>73.25</v>
       </c>
       <c r="H12">
-        <f>R12</f>
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="I12">
-        <f>S12</f>
+        <f t="shared" si="1"/>
         <v>71.5</v>
       </c>
       <c r="J12">
-        <f>T12</f>
+        <f t="shared" si="1"/>
         <v>71</v>
       </c>
       <c r="L12" t="s">
@@ -1152,42 +1149,42 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13">
-        <f>M13</f>
+        <f t="shared" si="1"/>
         <v>76.17</v>
       </c>
       <c r="D13">
-        <f>N13</f>
+        <f t="shared" si="1"/>
         <v>76.87</v>
       </c>
       <c r="E13">
-        <f>O13</f>
+        <f t="shared" si="1"/>
         <v>76.25</v>
       </c>
       <c r="F13">
-        <f>P13</f>
+        <f t="shared" si="1"/>
         <v>75.78</v>
       </c>
       <c r="G13">
-        <f>Q13</f>
+        <f t="shared" si="1"/>
         <v>76.48</v>
       </c>
       <c r="H13">
-        <f>R13</f>
+        <f t="shared" si="1"/>
         <v>75.19</v>
       </c>
       <c r="I13">
-        <f>S13</f>
+        <f t="shared" si="1"/>
         <v>74.59</v>
       </c>
       <c r="J13">
-        <f>T13</f>
+        <f t="shared" si="1"/>
         <v>74.12</v>
       </c>
       <c r="L13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M13">
         <v>76.17</v>
@@ -1222,35 +1219,35 @@
         <v>21</v>
       </c>
       <c r="C14">
-        <f>M14*10</f>
+        <f t="shared" ref="C14:J18" si="2">M14*10</f>
         <v>755</v>
       </c>
       <c r="D14">
-        <f>N14*10</f>
+        <f t="shared" si="2"/>
         <v>770.40000000000009</v>
       </c>
       <c r="E14">
-        <f>O14*10</f>
+        <f t="shared" si="2"/>
         <v>796.5</v>
       </c>
       <c r="F14">
-        <f>P14*10</f>
+        <f t="shared" si="2"/>
         <v>813.6</v>
       </c>
       <c r="G14">
-        <f>Q14*10</f>
+        <f t="shared" si="2"/>
         <v>827.4</v>
       </c>
       <c r="H14">
-        <f>R14*10</f>
+        <f t="shared" si="2"/>
         <v>844.30000000000007</v>
       </c>
       <c r="I14">
-        <f>S14*10</f>
+        <f t="shared" si="2"/>
         <v>861.5</v>
       </c>
       <c r="J14">
-        <f>T14*10</f>
+        <f t="shared" si="2"/>
         <v>877.5</v>
       </c>
       <c r="L14" t="s">
@@ -1289,35 +1286,35 @@
         <v>23</v>
       </c>
       <c r="C15">
-        <f>M15*10</f>
+        <f t="shared" si="2"/>
         <v>105</v>
       </c>
       <c r="D15">
-        <f>N15*10</f>
+        <f t="shared" si="2"/>
         <v>115</v>
       </c>
       <c r="E15">
-        <f>O15*10</f>
+        <f t="shared" si="2"/>
         <v>135</v>
       </c>
       <c r="F15">
-        <f>P15*10</f>
+        <f t="shared" si="2"/>
         <v>150</v>
       </c>
       <c r="G15">
-        <f>Q15*10</f>
+        <f t="shared" si="2"/>
         <v>165</v>
       </c>
       <c r="H15">
-        <f>R15*10</f>
+        <f t="shared" si="2"/>
         <v>180</v>
       </c>
       <c r="I15">
-        <f>S15*10</f>
+        <f t="shared" si="2"/>
         <v>195</v>
       </c>
       <c r="J15">
-        <f>T15*10</f>
+        <f t="shared" si="2"/>
         <v>215</v>
       </c>
       <c r="L15" t="s">
@@ -1356,35 +1353,35 @@
         <v>25</v>
       </c>
       <c r="C16">
-        <f>M16*10</f>
+        <f t="shared" si="2"/>
         <v>1036</v>
       </c>
       <c r="D16">
-        <f>N16*10</f>
+        <f t="shared" si="2"/>
         <v>1046.8000000000002</v>
       </c>
       <c r="E16">
-        <f>O16*10</f>
+        <f t="shared" si="2"/>
         <v>1054.0999999999999</v>
       </c>
       <c r="F16">
-        <f>P16*10</f>
+        <f t="shared" si="2"/>
         <v>1059.2</v>
       </c>
       <c r="G16">
-        <f>Q16*10</f>
+        <f t="shared" si="2"/>
         <v>1070.6999999999998</v>
       </c>
       <c r="H16">
-        <f>R16*10</f>
+        <f t="shared" si="2"/>
         <v>1081.7</v>
       </c>
       <c r="I16">
-        <f>S16*10</f>
+        <f t="shared" si="2"/>
         <v>1091.7</v>
       </c>
       <c r="J16">
-        <f>T16*10</f>
+        <f t="shared" si="2"/>
         <v>1107</v>
       </c>
       <c r="L16" t="s">
@@ -1423,35 +1420,35 @@
         <v>27</v>
       </c>
       <c r="C17">
-        <f>M17*10</f>
+        <f t="shared" si="2"/>
         <v>622.70000000000005</v>
       </c>
       <c r="D17">
-        <f>N17*10</f>
+        <f t="shared" si="2"/>
         <v>633.20000000000005</v>
       </c>
       <c r="E17">
-        <f>O17*10</f>
+        <f t="shared" si="2"/>
         <v>400.5</v>
       </c>
       <c r="F17">
-        <f>P17*10</f>
+        <f t="shared" si="2"/>
         <v>643.1</v>
       </c>
       <c r="G17">
-        <f>Q17*10</f>
+        <f t="shared" si="2"/>
         <v>654.4</v>
       </c>
       <c r="H17">
-        <f>R17*10</f>
+        <f t="shared" si="2"/>
         <v>665</v>
       </c>
       <c r="I17">
-        <f>S17*10</f>
+        <f t="shared" si="2"/>
         <v>673</v>
       </c>
       <c r="J17">
-        <f>T17*10</f>
+        <f t="shared" si="2"/>
         <v>688</v>
       </c>
       <c r="L17" t="s">
@@ -1490,35 +1487,35 @@
         <v>29</v>
       </c>
       <c r="C18">
-        <f>M18*10</f>
+        <f t="shared" si="2"/>
         <v>423</v>
       </c>
       <c r="D18">
-        <f>N18*10</f>
+        <f t="shared" si="2"/>
         <v>423</v>
       </c>
       <c r="E18">
-        <f>O18*10</f>
+        <f t="shared" si="2"/>
         <v>423</v>
       </c>
       <c r="F18">
-        <f>P18*10</f>
+        <f t="shared" si="2"/>
         <v>425</v>
       </c>
       <c r="G18">
-        <f>Q18*10</f>
+        <f t="shared" si="2"/>
         <v>425</v>
       </c>
       <c r="H18">
-        <f>R18*10</f>
+        <f t="shared" si="2"/>
         <v>425</v>
       </c>
       <c r="I18">
-        <f>S18*10</f>
+        <f t="shared" si="2"/>
         <v>427</v>
       </c>
       <c r="J18">
-        <f>T18*10</f>
+        <f t="shared" si="2"/>
         <v>427</v>
       </c>
       <c r="L18" t="s">
@@ -1557,35 +1554,35 @@
         <v>31</v>
       </c>
       <c r="C19">
-        <f>M19</f>
+        <f t="shared" ref="C19:J20" si="3">M19</f>
         <v>70</v>
       </c>
       <c r="D19">
-        <f>N19</f>
+        <f t="shared" si="3"/>
         <v>69</v>
       </c>
       <c r="E19">
-        <f>O19</f>
+        <f t="shared" si="3"/>
         <v>69</v>
       </c>
       <c r="F19">
-        <f>P19</f>
+        <f t="shared" si="3"/>
         <v>67</v>
       </c>
       <c r="G19">
-        <f>Q19</f>
+        <f t="shared" si="3"/>
         <v>67</v>
       </c>
       <c r="H19">
-        <f>R19</f>
+        <f t="shared" si="3"/>
         <v>65</v>
       </c>
       <c r="I19">
-        <f>S19</f>
+        <f t="shared" si="3"/>
         <v>65</v>
       </c>
       <c r="J19">
-        <f>T19</f>
+        <f t="shared" si="3"/>
         <v>65</v>
       </c>
       <c r="L19" t="s">
@@ -1624,35 +1621,35 @@
         <v>33</v>
       </c>
       <c r="C20">
-        <f>M20</f>
+        <f t="shared" si="3"/>
         <v>69.569999999999993</v>
       </c>
       <c r="D20">
-        <f>N20</f>
+        <f t="shared" si="3"/>
         <v>69.569999999999993</v>
       </c>
       <c r="E20">
-        <f>O20</f>
+        <f t="shared" si="3"/>
         <v>70.38</v>
       </c>
       <c r="F20">
-        <f>P20</f>
+        <f t="shared" si="3"/>
         <v>65.290000000000006</v>
       </c>
       <c r="G20">
-        <f>Q20</f>
+        <f t="shared" si="3"/>
         <v>66.98</v>
       </c>
       <c r="H20">
-        <f>R20</f>
+        <f t="shared" si="3"/>
         <v>65.290000000000006</v>
       </c>
       <c r="I20">
-        <f>S20</f>
+        <f t="shared" si="3"/>
         <v>61.92</v>
       </c>
       <c r="J20">
-        <f>T20</f>
+        <f t="shared" si="3"/>
         <v>61.92</v>
       </c>
       <c r="L20" t="s">
@@ -1691,35 +1688,35 @@
         <v>35</v>
       </c>
       <c r="C21">
-        <f>M21*10</f>
+        <f t="shared" ref="C21:J23" si="4">M21*10</f>
         <v>541.79999999999995</v>
       </c>
       <c r="D21">
-        <f>N21*10</f>
+        <f t="shared" si="4"/>
         <v>550.20000000000005</v>
       </c>
       <c r="E21">
-        <f>O21*10</f>
+        <f t="shared" si="4"/>
         <v>570</v>
       </c>
       <c r="F21">
-        <f>P21*10</f>
+        <f t="shared" si="4"/>
         <v>585.29999999999995</v>
       </c>
       <c r="G21">
-        <f>Q21*10</f>
+        <f t="shared" si="4"/>
         <v>598.5</v>
       </c>
       <c r="H21">
-        <f>R21*10</f>
+        <f t="shared" si="4"/>
         <v>611.70000000000005</v>
       </c>
       <c r="I21">
-        <f>S21*10</f>
+        <f t="shared" si="4"/>
         <v>628.1</v>
       </c>
       <c r="J21">
-        <f>T21*10</f>
+        <f t="shared" si="4"/>
         <v>647.09999999999991</v>
       </c>
       <c r="L21" t="s">
@@ -1758,35 +1755,35 @@
         <v>37</v>
       </c>
       <c r="C22">
-        <f>M22*10</f>
+        <f t="shared" si="4"/>
         <v>390.4</v>
       </c>
       <c r="D22">
-        <f>N22*10</f>
+        <f t="shared" si="4"/>
         <v>398</v>
       </c>
       <c r="E22">
-        <f>O22*10</f>
+        <f t="shared" si="4"/>
         <v>400.5</v>
       </c>
       <c r="F22">
-        <f>P22*10</f>
+        <f t="shared" si="4"/>
         <v>405</v>
       </c>
       <c r="G22">
-        <f>Q22*10</f>
+        <f t="shared" si="4"/>
         <v>409.3</v>
       </c>
       <c r="H22">
-        <f>R22*10</f>
+        <f t="shared" si="4"/>
         <v>417.5</v>
       </c>
       <c r="I22">
-        <f>S22*10</f>
+        <f t="shared" si="4"/>
         <v>425.5</v>
       </c>
       <c r="J22">
-        <f>T22*10</f>
+        <f t="shared" si="4"/>
         <v>434.6</v>
       </c>
       <c r="L22" t="s">
@@ -1825,35 +1822,35 @@
         <v>39</v>
       </c>
       <c r="C23">
-        <f>M23*10</f>
+        <f t="shared" si="4"/>
         <v>406</v>
       </c>
       <c r="D23">
-        <f>N23*10</f>
+        <f t="shared" si="4"/>
         <v>406</v>
       </c>
       <c r="E23">
-        <f>O23*10</f>
+        <f t="shared" si="4"/>
         <v>406</v>
       </c>
       <c r="F23">
-        <f>P23*10</f>
+        <f t="shared" si="4"/>
         <v>406</v>
       </c>
       <c r="G23">
-        <f>Q23*10</f>
+        <f t="shared" si="4"/>
         <v>406</v>
       </c>
       <c r="H23">
-        <f>R23*10</f>
+        <f t="shared" si="4"/>
         <v>406</v>
       </c>
       <c r="I23">
-        <f>S23*10</f>
+        <f t="shared" si="4"/>
         <v>406</v>
       </c>
       <c r="J23">
-        <f>T23*10</f>
+        <f t="shared" si="4"/>
         <v>406</v>
       </c>
       <c r="L23" t="s">
@@ -1892,35 +1889,35 @@
         <v>41</v>
       </c>
       <c r="C24">
-        <f>M24</f>
+        <f t="shared" ref="C24:J24" si="5">M24</f>
         <v>55.5</v>
       </c>
       <c r="D24">
-        <f>N24</f>
+        <f t="shared" si="5"/>
         <v>55.5</v>
       </c>
       <c r="E24">
-        <f>O24</f>
+        <f t="shared" si="5"/>
         <v>55.5</v>
       </c>
       <c r="F24">
-        <f>P24</f>
+        <f t="shared" si="5"/>
         <v>55.5</v>
       </c>
       <c r="G24">
-        <f>Q24</f>
+        <f t="shared" si="5"/>
         <v>55.5</v>
       </c>
       <c r="H24">
-        <f>R24</f>
+        <f t="shared" si="5"/>
         <v>55.5</v>
       </c>
       <c r="I24">
-        <f>S24</f>
+        <f t="shared" si="5"/>
         <v>55.5</v>
       </c>
       <c r="J24">
-        <f>T24</f>
+        <f t="shared" si="5"/>
         <v>55.5</v>
       </c>
       <c r="L24" t="s">
@@ -2078,26 +2075,26 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>101</v>
+      </c>
+      <c r="B36" t="s">
         <v>102</v>
-      </c>
-      <c r="B36" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37" t="s">
         <v>104</v>
-      </c>
-      <c r="B37" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -2141,47 +2138,41 @@
       <c r="A44" t="s">
         <v>62</v>
       </c>
-      <c r="B44" t="s">
-        <v>63</v>
-      </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>64</v>
-      </c>
-      <c r="B45">
-        <v>40</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>67</v>
+      </c>
+      <c r="B48" t="s">
         <v>68</v>
-      </c>
-      <c r="B48" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>69</v>
+      </c>
+      <c r="B49" t="s">
         <v>70</v>
-      </c>
-      <c r="B49" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B50">
         <v>44</v>
@@ -2189,53 +2180,53 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>71</v>
+      </c>
+      <c r="B56" t="s">
         <v>72</v>
-      </c>
-      <c r="B56" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>74</v>
+      </c>
+      <c r="B58" t="s">
         <v>75</v>
-      </c>
-      <c r="B58" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B59" t="s">
         <v>56</v>
@@ -2243,15 +2234,15 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>77</v>
+      </c>
+      <c r="B60" t="s">
         <v>78</v>
-      </c>
-      <c r="B60" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B61">
         <v>48</v>
@@ -2259,80 +2250,80 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>83</v>
+      </c>
+      <c r="B65" t="s">
         <v>84</v>
-      </c>
-      <c r="B65" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B66" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>88</v>
+      </c>
+      <c r="B69" t="s">
         <v>89</v>
-      </c>
-      <c r="B69" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>90</v>
+      </c>
+      <c r="B70" t="s">
         <v>91</v>
-      </c>
-      <c r="B70" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B71" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>56</v>
@@ -2340,17 +2331,17 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B76">
         <v>6000</v>
@@ -2358,28 +2349,28 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>106</v>
+      </c>
+      <c r="B80" t="s">
         <v>107</v>
-      </c>
-      <c r="B80" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>
